--- a/doc.xlsx
+++ b/doc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="5" activeTab="11"/>
+    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="5" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="SQLite" sheetId="3" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="860">
   <si>
     <t>DB名</t>
   </si>
@@ -277,7 +277,7 @@
     <t>venue</t>
   </si>
   <si>
-    <t xml:space="preserve">INSERT INTO MATCHES (match_id, match_kbn, match_date, venue) VALUES </t>
+    <t>INSERT INTO MATCHES (match_id, match_kbn, match_date, venue) VALUES</t>
   </si>
   <si>
     <t>001</t>
@@ -1300,7 +1300,7 @@
     <t>group_name</t>
   </si>
   <si>
-    <t xml:space="preserve">INSERT INTO GROUPSTAGE (group_id, group_name) VALUES </t>
+    <t>INSERT INTO GROUPSTAGE (group_id, group_name) VALUES</t>
   </si>
   <si>
     <t>01</t>
@@ -1384,7 +1384,7 @@
     <t>team_name</t>
   </si>
   <si>
-    <t xml:space="preserve">INSERT INTO TEAM (team_id, team_name, group_id) VALUES </t>
+    <t>INSERT INTO TEAM (team_id, team_name, group_id) VALUES</t>
   </si>
   <si>
     <t>チーム名</t>
@@ -1396,7 +1396,7 @@
     <t>--work　日本語名</t>
   </si>
   <si>
-    <t xml:space="preserve">INSERT INTO FIFARANK (fifarank, team_id) VALUES </t>
+    <t>INSERT INTO FIFARANK (fifarank, team_id) VALUES</t>
   </si>
   <si>
     <t>ITA</t>
@@ -2500,28 +2500,52 @@
     <t>→変数grouplistへ</t>
   </si>
   <si>
+    <t>STEP0で順位が確定したもの</t>
+  </si>
+  <si>
     <t>グループの順位表　STEP1の結果</t>
   </si>
   <si>
+    <t>STEP1のテーブルに入れる</t>
+  </si>
+  <si>
     <t>grouplistが終わるまで繰り返し</t>
   </si>
   <si>
     <t>GROUP_RANK0から、rank, team_idを取得する（SQL）</t>
   </si>
   <si>
+    <t>順位が確定していないもの</t>
+  </si>
+  <si>
     <t>→変数gr0listへ</t>
   </si>
   <si>
+    <t>順位がつかなくなるまで繰り返し</t>
+  </si>
+  <si>
+    <t>リストアップする</t>
+  </si>
+  <si>
     <t>同率順位をカウントする</t>
   </si>
   <si>
+    <t>STEP1の順位付けをする</t>
+  </si>
+  <si>
     <t>→結果を変数countsへ</t>
   </si>
   <si>
+    <t>順位が確定したもの</t>
+  </si>
+  <si>
     <t>countsが終わるまで繰り返し</t>
   </si>
   <si>
     <t>値が1（同率がいない）ならGROUP_RANK1へINSERT</t>
+  </si>
+  <si>
+    <t>順位がつかない（処理前と変わってない）ならループ終了</t>
   </si>
   <si>
     <t>そうでなければ同率のものを変数tiedlistへ格納</t>
@@ -4407,7 +4431,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:S36"/>
+  <dimension ref="B2:AJ36"/>
   <sheetFormatPr defaultColWidth="3.77777777777778" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.77777777777778" customWidth="1"/>
@@ -4417,7 +4441,7 @@
     <col min="6" max="6" width="3.77777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17">
+    <row r="2" spans="2:34">
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
@@ -4426,11 +4450,11 @@
       <c r="E2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="AH2" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="3" spans="2:17">
+    <row r="3" spans="2:34">
       <c r="B3" s="3" t="s">
         <v>57</v>
       </c>
@@ -4439,11 +4463,11 @@
       <c r="E3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="AH3" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:18">
       <c r="B4" s="1" t="s">
         <v>39</v>
       </c>
@@ -4453,10 +4477,13 @@
       <c r="H4" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="5" spans="2:17">
+      <c r="R4" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="5" spans="2:34">
       <c r="B5" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -4464,19 +4491,22 @@
       <c r="I5" t="s">
         <v>778</v>
       </c>
-      <c r="Q5" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="6" spans="9:18">
+      <c r="S5" t="s">
+        <v>812</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="6" spans="9:35">
       <c r="I6" t="s">
         <v>779</v>
       </c>
-      <c r="R6" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18">
+      <c r="AI6" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="7" spans="2:35">
       <c r="B7" s="5" t="s">
         <v>83</v>
       </c>
@@ -4493,10 +4523,13 @@
         <v>780</v>
       </c>
       <c r="R7" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9">
+        <v>815</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19">
       <c r="B8" s="10" t="s">
         <v>408</v>
       </c>
@@ -4512,8 +4545,11 @@
       <c r="I8" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="9" spans="2:18">
+      <c r="S8" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="9" spans="2:35">
       <c r="B9" s="10" t="s">
         <v>782</v>
       </c>
@@ -4526,11 +4562,14 @@
         <f>B9&amp;", "</f>
         <v>rank,</v>
       </c>
-      <c r="R9" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18">
+      <c r="T9" t="s">
+        <v>818</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="10" spans="2:35">
       <c r="B10" s="10" t="s">
         <v>294</v>
       </c>
@@ -4543,8 +4582,11 @@
         <f>B10&amp;", "</f>
         <v>team_id,</v>
       </c>
-      <c r="R10" t="s">
-        <v>815</v>
+      <c r="T10" t="s">
+        <v>820</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>821</v>
       </c>
     </row>
     <row r="11" spans="2:6">
@@ -4561,7 +4603,7 @@
         <v>played,</v>
       </c>
     </row>
-    <row r="12" spans="2:18">
+    <row r="12" spans="2:35">
       <c r="B12" s="10" t="s">
         <v>789</v>
       </c>
@@ -4574,11 +4616,14 @@
         <f t="shared" si="0"/>
         <v>win,</v>
       </c>
-      <c r="R12" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19">
+      <c r="T12" t="s">
+        <v>822</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="13" spans="2:36">
       <c r="B13" s="10" t="s">
         <v>791</v>
       </c>
@@ -4591,8 +4636,11 @@
         <f t="shared" si="0"/>
         <v>draw,</v>
       </c>
-      <c r="S13" t="s">
-        <v>817</v>
+      <c r="U13" t="s">
+        <v>812</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="14" spans="2:6">
@@ -4609,7 +4657,7 @@
         <v>loss,</v>
       </c>
     </row>
-    <row r="15" spans="2:19">
+    <row r="15" spans="2:36">
       <c r="B15" s="10" t="s">
         <v>797</v>
       </c>
@@ -4622,8 +4670,11 @@
         <f t="shared" si="0"/>
         <v>goal_scored,</v>
       </c>
-      <c r="S15" t="s">
-        <v>818</v>
+      <c r="T15" t="s">
+        <v>825</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="16" spans="2:6">
@@ -4654,7 +4705,7 @@
         <v>goal_difference,</v>
       </c>
     </row>
-    <row r="18" spans="2:17">
+    <row r="18" spans="2:34">
       <c r="B18" s="10" t="s">
         <v>297</v>
       </c>
@@ -4667,11 +4718,11 @@
         <f t="shared" si="0"/>
         <v>conduct_score,</v>
       </c>
-      <c r="Q18" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17">
+      <c r="AH18" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="19" spans="2:34">
       <c r="B19" s="10" t="s">
         <v>805</v>
       </c>
@@ -4684,11 +4735,11 @@
         <f t="shared" si="0"/>
         <v>points,</v>
       </c>
-      <c r="Q19" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17">
+      <c r="AH19" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="20" spans="2:34">
       <c r="B20" s="10" t="s">
         <v>440</v>
       </c>
@@ -4701,68 +4752,68 @@
         <f>B20</f>
         <v>fifarank</v>
       </c>
-      <c r="Q20" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="21" spans="17:17">
-      <c r="Q21" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="22" spans="17:17">
-      <c r="Q22" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="26" spans="17:17">
-      <c r="Q26" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="27" spans="17:17">
-      <c r="Q27" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="28" spans="17:17">
-      <c r="Q28" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="29" spans="17:17">
-      <c r="Q29" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="30" spans="17:17">
-      <c r="Q30" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="31" spans="17:17">
-      <c r="Q31" t="s">
+      <c r="AH20" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="32" spans="17:17">
-      <c r="Q32" t="s">
+    <row r="21" spans="34:34">
+      <c r="AH21" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="33" spans="17:17">
-      <c r="Q33" t="s">
+    <row r="22" spans="34:34">
+      <c r="AH22" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="35" spans="17:17">
-      <c r="Q35" t="s">
+    <row r="26" spans="34:34">
+      <c r="AH26" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="36" spans="17:17">
-      <c r="Q36" t="s">
+    <row r="27" spans="34:34">
+      <c r="AH27" t="s">
         <v>833</v>
+      </c>
+    </row>
+    <row r="28" spans="34:34">
+      <c r="AH28" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="29" spans="34:34">
+      <c r="AH29" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="30" spans="34:34">
+      <c r="AH30" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="31" spans="34:34">
+      <c r="AH31" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="32" spans="34:34">
+      <c r="AH32" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="33" spans="34:34">
+      <c r="AH33" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="35" spans="34:34">
+      <c r="AH35" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="36" spans="34:34">
+      <c r="AH36" t="s">
+        <v>841</v>
       </c>
     </row>
   </sheetData>
@@ -4815,7 +4866,7 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="3" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -5030,7 +5081,7 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="3" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -5216,7 +5267,7 @@
         <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
     </row>
     <row r="3" spans="2:7">
@@ -5229,7 +5280,7 @@
         <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
     </row>
     <row r="4" spans="2:7">
@@ -5240,12 +5291,12 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="G4" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="3" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -5409,12 +5460,12 @@
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="6" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="6" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -5422,7 +5473,7 @@
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -5430,7 +5481,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -5438,17 +5489,17 @@
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="6" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="6" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
     </row>
     <row r="13" spans="2:5">
@@ -5456,17 +5507,17 @@
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="6" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="6" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
     </row>
     <row r="15" spans="2:5">
@@ -5474,7 +5525,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
     </row>
     <row r="16" spans="2:5">
@@ -5482,7 +5533,7 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
     </row>
   </sheetData>
@@ -12872,12 +12923,18 @@
       <c r="H205" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="I205" s="17"/>
-      <c r="J205" s="17"/>
-      <c r="K205" s="17"/>
+      <c r="I205" s="17">
+        <v>1</v>
+      </c>
+      <c r="J205" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="K205" s="17">
+        <v>-1</v>
+      </c>
       <c r="L205" t="str">
         <f t="shared" si="3"/>
-        <v>	('102', 'ENG', , , ),</v>
+        <v>	('102', 'ENG', 1, NULL, -1),</v>
       </c>
       <c r="M205" t="s">
         <v>397</v>
@@ -12890,12 +12947,18 @@
       <c r="H206" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="I206" s="17"/>
-      <c r="J206" s="17"/>
-      <c r="K206" s="17"/>
+      <c r="I206" s="17">
+        <v>2</v>
+      </c>
+      <c r="J206" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="K206" s="17">
+        <v>-3</v>
+      </c>
       <c r="L206" t="str">
         <f t="shared" si="3"/>
-        <v>	('102', 'ARG', , , ),</v>
+        <v>	('102', 'ARG', 2, NULL, -3),</v>
       </c>
       <c r="M206" t="s">
         <v>385</v>
@@ -12923,13 +12986,15 @@
       <c r="G208" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="H208" s="16"/>
+      <c r="H208" s="16" t="s">
+        <v>396</v>
+      </c>
       <c r="I208" s="17"/>
       <c r="J208" s="17"/>
       <c r="K208" s="17"/>
       <c r="L208" t="str">
         <f t="shared" si="3"/>
-        <v>	('103', '', , , ),</v>
+        <v>	('103', 'ENG', , , ),</v>
       </c>
     </row>
     <row r="209" spans="7:13">
@@ -12954,13 +13019,15 @@
       <c r="G210" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="H210" s="16"/>
+      <c r="H210" s="16" t="s">
+        <v>384</v>
+      </c>
       <c r="I210" s="17"/>
       <c r="J210" s="17"/>
       <c r="K210" s="17"/>
       <c r="L210" t="str">
         <f>CHAR(9)&amp;"('"&amp;G210&amp;"', '"&amp;H210&amp;"', "&amp;I210&amp;", "&amp;J210&amp;", "&amp;K210&amp;")"</f>
-        <v>	('104', '', , , )</v>
+        <v>	('104', 'ARG', , , )</v>
       </c>
     </row>
     <row r="211" spans="12:12">
@@ -13026,8 +13093,8 @@
         <v>412</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I13" si="0">CHAR(9)&amp;"('"&amp;G3&amp;"', '"&amp;H3&amp;"'), "</f>
-        <v>('01', 'A'),</v>
+        <f t="shared" ref="I3:I13" si="0">CHAR(9)&amp;"('"&amp;G3&amp;"', '"&amp;H3&amp;"'),"</f>
+        <v>	('01', 'A'),</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -13045,7 +13112,7 @@
       </c>
       <c r="I4" t="str">
         <f t="shared" si="0"/>
-        <v>('02', 'B'),</v>
+        <v>	('02', 'B'),</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -13063,7 +13130,7 @@
       </c>
       <c r="I5" t="str">
         <f t="shared" si="0"/>
-        <v>('03', 'C'),</v>
+        <v>	('03', 'C'),</v>
       </c>
     </row>
     <row r="6" spans="7:9">
@@ -13075,7 +13142,7 @@
       </c>
       <c r="I6" t="str">
         <f t="shared" si="0"/>
-        <v>('04', 'D'),</v>
+        <v>	('04', 'D'),</v>
       </c>
     </row>
     <row r="7" spans="2:9">
@@ -13099,7 +13166,7 @@
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>('05', 'E'),</v>
+        <v>	('05', 'E'),</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -13123,7 +13190,7 @@
       </c>
       <c r="I8" t="str">
         <f t="shared" si="0"/>
-        <v>('06', 'F'),</v>
+        <v>	('06', 'F'),</v>
       </c>
     </row>
     <row r="9" spans="2:9">
@@ -13145,7 +13212,7 @@
       </c>
       <c r="I9" t="str">
         <f t="shared" si="0"/>
-        <v>('07', 'G'),</v>
+        <v>	('07', 'G'),</v>
       </c>
     </row>
     <row r="10" spans="2:9">
@@ -13161,7 +13228,7 @@
       </c>
       <c r="I10" t="str">
         <f t="shared" si="0"/>
-        <v>('08', 'H'),</v>
+        <v>	('08', 'H'),</v>
       </c>
     </row>
     <row r="11" spans="2:9">
@@ -13177,7 +13244,7 @@
       </c>
       <c r="I11" t="str">
         <f t="shared" si="0"/>
-        <v>('09', 'I'),</v>
+        <v>	('09', 'I'),</v>
       </c>
     </row>
     <row r="12" spans="2:9">
@@ -13193,7 +13260,7 @@
       </c>
       <c r="I12" t="str">
         <f t="shared" si="0"/>
-        <v>('10', 'J'),</v>
+        <v>	('10', 'J'),</v>
       </c>
     </row>
     <row r="13" spans="7:9">
@@ -13205,7 +13272,7 @@
       </c>
       <c r="I13" t="str">
         <f t="shared" si="0"/>
-        <v>('11', 'K'),</v>
+        <v>	('11', 'K'),</v>
       </c>
     </row>
     <row r="14" spans="7:9">
@@ -13217,7 +13284,7 @@
       </c>
       <c r="I14" t="str">
         <f>CHAR(9)&amp;"('"&amp;G14&amp;"', '"&amp;H14&amp;"')"</f>
-        <v>('12', 'L')</v>
+        <v>	('12', 'L')</v>
       </c>
     </row>
     <row r="15" spans="9:9">
@@ -13290,8 +13357,8 @@
         <v>411</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J49" si="0">CHAR(9)&amp;"('"&amp;G3&amp;"', '"&amp;H3&amp;"', '"&amp;I3&amp;"'), "</f>
-        <v>('MEX', 'メキシコ', '01'),</v>
+        <f t="shared" ref="J3:J49" si="0">CHAR(9)&amp;"('"&amp;G3&amp;"', '"&amp;H3&amp;"', '"&amp;I3&amp;"'),"</f>
+        <v>	('MEX', 'メキシコ', '01'),</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -13312,7 +13379,7 @@
       </c>
       <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>('KOR', '大韓民国', '01'),</v>
+        <v>	('KOR', '大韓民国', '01'),</v>
       </c>
     </row>
     <row r="5" spans="2:10">
@@ -13333,7 +13400,7 @@
       </c>
       <c r="J5" t="str">
         <f t="shared" si="0"/>
-        <v>('CZE', 'チェコ共和国', '01'),</v>
+        <v>	('CZE', 'チェコ共和国', '01'),</v>
       </c>
     </row>
     <row r="6" spans="7:10">
@@ -13348,7 +13415,7 @@
       </c>
       <c r="J6" t="str">
         <f t="shared" si="0"/>
-        <v>('RSA', '南アフリカ', '01'),</v>
+        <v>	('RSA', '南アフリカ', '01'),</v>
       </c>
     </row>
     <row r="7" spans="2:10">
@@ -13375,7 +13442,7 @@
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>('CAN', 'カナダ', '02'),</v>
+        <v>	('CAN', 'カナダ', '02'),</v>
       </c>
     </row>
     <row r="8" spans="2:10">
@@ -13402,7 +13469,7 @@
       </c>
       <c r="J8" t="str">
         <f t="shared" si="0"/>
-        <v>('SUI', 'スイス', '02'),</v>
+        <v>	('SUI', 'スイス', '02'),</v>
       </c>
     </row>
     <row r="9" spans="2:10">
@@ -13427,7 +13494,7 @@
       </c>
       <c r="J9" t="str">
         <f t="shared" si="0"/>
-        <v>('BIH', 'ボスニア・ヘルツェゴビナ', '02'),</v>
+        <v>	('BIH', 'ボスニア・ヘルツェゴビナ', '02'),</v>
       </c>
     </row>
     <row r="10" spans="2:10">
@@ -13452,7 +13519,7 @@
       </c>
       <c r="J10" t="str">
         <f t="shared" si="0"/>
-        <v>('QAT', 'カタール', '02'),</v>
+        <v>	('QAT', 'カタール', '02'),</v>
       </c>
     </row>
     <row r="11" spans="2:10">
@@ -13471,7 +13538,7 @@
       </c>
       <c r="J11" t="str">
         <f t="shared" si="0"/>
-        <v>('BRA', 'ブラジル', '03'),</v>
+        <v>	('BRA', 'ブラジル', '03'),</v>
       </c>
     </row>
     <row r="12" spans="2:10">
@@ -13490,7 +13557,7 @@
       </c>
       <c r="J12" t="str">
         <f t="shared" si="0"/>
-        <v>('MAR', 'モロッコ', '03'),</v>
+        <v>	('MAR', 'モロッコ', '03'),</v>
       </c>
     </row>
     <row r="13" spans="7:10">
@@ -13505,7 +13572,7 @@
       </c>
       <c r="J13" t="str">
         <f t="shared" si="0"/>
-        <v>('SCO', 'スコットランド', '03'),</v>
+        <v>	('SCO', 'スコットランド', '03'),</v>
       </c>
     </row>
     <row r="14" spans="7:10">
@@ -13520,7 +13587,7 @@
       </c>
       <c r="J14" t="str">
         <f t="shared" si="0"/>
-        <v>('HAI', 'ハイチ', '03'),</v>
+        <v>	('HAI', 'ハイチ', '03'),</v>
       </c>
     </row>
     <row r="15" spans="7:10">
@@ -13535,7 +13602,7 @@
       </c>
       <c r="J15" t="str">
         <f t="shared" si="0"/>
-        <v>('USA', 'アメリカ合衆国', '04'),</v>
+        <v>	('USA', 'アメリカ合衆国', '04'),</v>
       </c>
     </row>
     <row r="16" spans="7:10">
@@ -13550,7 +13617,7 @@
       </c>
       <c r="J16" t="str">
         <f t="shared" si="0"/>
-        <v>('AUS', 'オーストラリア', '04'),</v>
+        <v>	('AUS', 'オーストラリア', '04'),</v>
       </c>
     </row>
     <row r="17" spans="7:10">
@@ -13565,7 +13632,7 @@
       </c>
       <c r="J17" t="str">
         <f t="shared" si="0"/>
-        <v>('PAR', 'パラグアイ', '04'),</v>
+        <v>	('PAR', 'パラグアイ', '04'),</v>
       </c>
     </row>
     <row r="18" spans="7:10">
@@ -13580,7 +13647,7 @@
       </c>
       <c r="J18" t="str">
         <f t="shared" si="0"/>
-        <v>('TUR', 'トルコ', '04'),</v>
+        <v>	('TUR', 'トルコ', '04'),</v>
       </c>
     </row>
     <row r="19" spans="7:10">
@@ -13595,7 +13662,7 @@
       </c>
       <c r="J19" t="str">
         <f t="shared" si="0"/>
-        <v>('GER', 'ドイツ', '05'),</v>
+        <v>	('GER', 'ドイツ', '05'),</v>
       </c>
     </row>
     <row r="20" spans="7:10">
@@ -13610,7 +13677,7 @@
       </c>
       <c r="J20" t="str">
         <f t="shared" si="0"/>
-        <v>('CIV', 'コートジボワール', '05'),</v>
+        <v>	('CIV', 'コートジボワール', '05'),</v>
       </c>
     </row>
     <row r="21" spans="7:10">
@@ -13625,7 +13692,7 @@
       </c>
       <c r="J21" t="str">
         <f t="shared" si="0"/>
-        <v>('ECU', 'エクアドル', '05'),</v>
+        <v>	('ECU', 'エクアドル', '05'),</v>
       </c>
     </row>
     <row r="22" spans="7:10">
@@ -13640,7 +13707,7 @@
       </c>
       <c r="J22" t="str">
         <f t="shared" si="0"/>
-        <v>('CUW', 'キュラソー', '05'),</v>
+        <v>	('CUW', 'キュラソー', '05'),</v>
       </c>
     </row>
     <row r="23" spans="7:10">
@@ -13655,7 +13722,7 @@
       </c>
       <c r="J23" t="str">
         <f t="shared" si="0"/>
-        <v>('NED', 'オランダ', '06'),</v>
+        <v>	('NED', 'オランダ', '06'),</v>
       </c>
     </row>
     <row r="24" spans="7:10">
@@ -13670,7 +13737,7 @@
       </c>
       <c r="J24" t="str">
         <f t="shared" si="0"/>
-        <v>('JPN', '日本', '06'),</v>
+        <v>	('JPN', '日本', '06'),</v>
       </c>
     </row>
     <row r="25" spans="7:10">
@@ -13685,7 +13752,7 @@
       </c>
       <c r="J25" t="str">
         <f t="shared" si="0"/>
-        <v>('SWE', 'スウェーデン', '06'),</v>
+        <v>	('SWE', 'スウェーデン', '06'),</v>
       </c>
     </row>
     <row r="26" spans="7:10">
@@ -13700,7 +13767,7 @@
       </c>
       <c r="J26" t="str">
         <f t="shared" si="0"/>
-        <v>('TUN', 'チュニジア', '06'),</v>
+        <v>	('TUN', 'チュニジア', '06'),</v>
       </c>
     </row>
     <row r="27" spans="7:10">
@@ -13715,7 +13782,7 @@
       </c>
       <c r="J27" t="str">
         <f t="shared" si="0"/>
-        <v>('EGY', 'エジプト', '07'),</v>
+        <v>	('EGY', 'エジプト', '07'),</v>
       </c>
     </row>
     <row r="28" spans="7:10">
@@ -13730,7 +13797,7 @@
       </c>
       <c r="J28" t="str">
         <f t="shared" si="0"/>
-        <v>('IRN', 'イラン', '07'),</v>
+        <v>	('IRN', 'イラン', '07'),</v>
       </c>
     </row>
     <row r="29" spans="7:10">
@@ -13745,7 +13812,7 @@
       </c>
       <c r="J29" t="str">
         <f t="shared" si="0"/>
-        <v>('BEL', 'ベルギー', '07'),</v>
+        <v>	('BEL', 'ベルギー', '07'),</v>
       </c>
     </row>
     <row r="30" spans="7:10">
@@ -13760,7 +13827,7 @@
       </c>
       <c r="J30" t="str">
         <f t="shared" si="0"/>
-        <v>('NZL', 'ニュージーランド', '07'),</v>
+        <v>	('NZL', 'ニュージーランド', '07'),</v>
       </c>
     </row>
     <row r="31" spans="7:10">
@@ -13775,7 +13842,7 @@
       </c>
       <c r="J31" t="str">
         <f t="shared" si="0"/>
-        <v>('ESP', 'スペイン', '08'),</v>
+        <v>	('ESP', 'スペイン', '08'),</v>
       </c>
     </row>
     <row r="32" spans="7:10">
@@ -13790,7 +13857,7 @@
       </c>
       <c r="J32" t="str">
         <f t="shared" si="0"/>
-        <v>('URU', 'ウルグアイ', '08'),</v>
+        <v>	('URU', 'ウルグアイ', '08'),</v>
       </c>
     </row>
     <row r="33" spans="7:10">
@@ -13805,7 +13872,7 @@
       </c>
       <c r="J33" t="str">
         <f t="shared" si="0"/>
-        <v>('CPV', 'カーボベルデ', '08'),</v>
+        <v>	('CPV', 'カーボベルデ', '08'),</v>
       </c>
     </row>
     <row r="34" spans="7:10">
@@ -13820,7 +13887,7 @@
       </c>
       <c r="J34" t="str">
         <f t="shared" si="0"/>
-        <v>('KSA', 'サウジアラビア', '08'),</v>
+        <v>	('KSA', 'サウジアラビア', '08'),</v>
       </c>
     </row>
     <row r="35" spans="7:10">
@@ -13835,7 +13902,7 @@
       </c>
       <c r="J35" t="str">
         <f t="shared" si="0"/>
-        <v>('FRA', 'フランス', '09'),</v>
+        <v>	('FRA', 'フランス', '09'),</v>
       </c>
     </row>
     <row r="36" spans="7:10">
@@ -13850,7 +13917,7 @@
       </c>
       <c r="J36" t="str">
         <f t="shared" si="0"/>
-        <v>('NOR', 'ノルウェー', '09'),</v>
+        <v>	('NOR', 'ノルウェー', '09'),</v>
       </c>
     </row>
     <row r="37" spans="7:10">
@@ -13865,7 +13932,7 @@
       </c>
       <c r="J37" t="str">
         <f t="shared" si="0"/>
-        <v>('SEN', 'セネガル', '09'),</v>
+        <v>	('SEN', 'セネガル', '09'),</v>
       </c>
     </row>
     <row r="38" spans="7:10">
@@ -13880,7 +13947,7 @@
       </c>
       <c r="J38" t="str">
         <f t="shared" si="0"/>
-        <v>('IRQ', 'イラク', '09'),</v>
+        <v>	('IRQ', 'イラク', '09'),</v>
       </c>
     </row>
     <row r="39" spans="7:10">
@@ -13895,7 +13962,7 @@
       </c>
       <c r="J39" t="str">
         <f t="shared" si="0"/>
-        <v>('ARG', 'アルゼンチン', '10'),</v>
+        <v>	('ARG', 'アルゼンチン', '10'),</v>
       </c>
     </row>
     <row r="40" spans="7:10">
@@ -13910,7 +13977,7 @@
       </c>
       <c r="J40" t="str">
         <f t="shared" si="0"/>
-        <v>('AUT', 'オーストリア', '10'),</v>
+        <v>	('AUT', 'オーストリア', '10'),</v>
       </c>
     </row>
     <row r="41" spans="7:10">
@@ -13925,7 +13992,7 @@
       </c>
       <c r="J41" t="str">
         <f t="shared" si="0"/>
-        <v>('JOR', 'ヨルダン', '10'),</v>
+        <v>	('JOR', 'ヨルダン', '10'),</v>
       </c>
     </row>
     <row r="42" spans="7:10">
@@ -13940,7 +14007,7 @@
       </c>
       <c r="J42" t="str">
         <f t="shared" si="0"/>
-        <v>('ALG', 'アルジェリア', '10'),</v>
+        <v>	('ALG', 'アルジェリア', '10'),</v>
       </c>
     </row>
     <row r="43" spans="7:10">
@@ -13955,7 +14022,7 @@
       </c>
       <c r="J43" t="str">
         <f t="shared" si="0"/>
-        <v>('COL', 'コロンビア', '11'),</v>
+        <v>	('COL', 'コロンビア', '11'),</v>
       </c>
     </row>
     <row r="44" spans="7:10">
@@ -13970,7 +14037,7 @@
       </c>
       <c r="J44" t="str">
         <f t="shared" si="0"/>
-        <v>('COD', 'コンゴ民主共和国', '11'),</v>
+        <v>	('COD', 'コンゴ民主共和国', '11'),</v>
       </c>
     </row>
     <row r="45" spans="7:10">
@@ -13985,7 +14052,7 @@
       </c>
       <c r="J45" t="str">
         <f t="shared" si="0"/>
-        <v>('POR', 'ポルトガル', '11'),</v>
+        <v>	('POR', 'ポルトガル', '11'),</v>
       </c>
     </row>
     <row r="46" spans="7:10">
@@ -14000,7 +14067,7 @@
       </c>
       <c r="J46" t="str">
         <f t="shared" si="0"/>
-        <v>('UZB', 'ウズベキスタン', '11'),</v>
+        <v>	('UZB', 'ウズベキスタン', '11'),</v>
       </c>
     </row>
     <row r="47" spans="7:10">
@@ -14015,7 +14082,7 @@
       </c>
       <c r="J47" t="str">
         <f t="shared" si="0"/>
-        <v>('ENG', 'イングランド', '12'),</v>
+        <v>	('ENG', 'イングランド', '12'),</v>
       </c>
     </row>
     <row r="48" spans="7:10">
@@ -14030,7 +14097,7 @@
       </c>
       <c r="J48" t="str">
         <f t="shared" si="0"/>
-        <v>('GHA', 'ガーナ', '12'),</v>
+        <v>	('GHA', 'ガーナ', '12'),</v>
       </c>
     </row>
     <row r="49" spans="7:10">
@@ -14045,7 +14112,7 @@
       </c>
       <c r="J49" t="str">
         <f t="shared" si="0"/>
-        <v>('PAN', 'パナマ', '12'),</v>
+        <v>	('PAN', 'パナマ', '12'),</v>
       </c>
     </row>
     <row r="50" spans="7:10">
@@ -14060,7 +14127,7 @@
       </c>
       <c r="J50" t="str">
         <f>CHAR(9)&amp;"('"&amp;G50&amp;"', '"&amp;H50&amp;"', '"&amp;I50&amp;"')"</f>
-        <v>('CRO', 'クロアチア', '12')</v>
+        <v>	('CRO', 'クロアチア', '12')</v>
       </c>
     </row>
     <row r="51" spans="10:10">
@@ -14133,8 +14200,8 @@
         <v>385</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J66" si="0">CHAR(9)&amp;"("&amp;G3&amp;", '"&amp;H3&amp;"'), "</f>
-        <v>(1, 'ARG'),</v>
+        <f>CHAR(9)&amp;"("&amp;G3&amp;", '"&amp;H3&amp;"'),"</f>
+        <v>	(1, 'ARG'),</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -14154,8 +14221,8 @@
         <v>361</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
-        <v>(2, 'ESP'),</v>
+        <f t="shared" ref="J3:J66" si="0">CHAR(9)&amp;"("&amp;G4&amp;", '"&amp;H4&amp;"'),"</f>
+        <v>	(2, 'ESP'),</v>
       </c>
     </row>
     <row r="5" spans="2:10">
@@ -14176,7 +14243,7 @@
       </c>
       <c r="J5" t="str">
         <f t="shared" si="0"/>
-        <v>(3, 'FRA'),</v>
+        <v>	(3, 'FRA'),</v>
       </c>
     </row>
     <row r="6" spans="7:10">
@@ -14191,7 +14258,7 @@
       </c>
       <c r="J6" t="str">
         <f t="shared" si="0"/>
-        <v>(4, 'ENG'),</v>
+        <v>	(4, 'ENG'),</v>
       </c>
     </row>
     <row r="7" spans="2:10">
@@ -14218,7 +14285,7 @@
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>(5, 'POR'),</v>
+        <v>	(5, 'POR'),</v>
       </c>
     </row>
     <row r="8" spans="2:10">
@@ -14245,7 +14312,7 @@
       </c>
       <c r="J8" t="str">
         <f t="shared" si="0"/>
-        <v>(6, 'BRA'),</v>
+        <v>	(6, 'BRA'),</v>
       </c>
     </row>
     <row r="9" spans="2:10">
@@ -14272,7 +14339,7 @@
       </c>
       <c r="J9" t="str">
         <f t="shared" si="0"/>
-        <v>(7, 'MAR'),</v>
+        <v>	(7, 'MAR'),</v>
       </c>
     </row>
     <row r="10" spans="2:10">
@@ -14291,7 +14358,7 @@
       </c>
       <c r="J10" t="str">
         <f t="shared" si="0"/>
-        <v>(8, 'NED'),</v>
+        <v>	(8, 'NED'),</v>
       </c>
     </row>
     <row r="11" spans="2:10">
@@ -14310,7 +14377,7 @@
       </c>
       <c r="J11" t="str">
         <f t="shared" si="0"/>
-        <v>(9, 'BEL'),</v>
+        <v>	(9, 'BEL'),</v>
       </c>
     </row>
     <row r="12" spans="2:10">
@@ -14329,7 +14396,7 @@
       </c>
       <c r="J12" t="str">
         <f t="shared" si="0"/>
-        <v>(10, 'GER'),</v>
+        <v>	(10, 'GER'),</v>
       </c>
     </row>
     <row r="13" spans="7:10">
@@ -14344,7 +14411,7 @@
       </c>
       <c r="J13" t="str">
         <f t="shared" si="0"/>
-        <v>(11, 'CRO'),</v>
+        <v>	(11, 'CRO'),</v>
       </c>
     </row>
     <row r="14" spans="7:10">
@@ -14359,7 +14426,7 @@
       </c>
       <c r="J14" t="str">
         <f t="shared" si="0"/>
-        <v>(12, 'ITA'),</v>
+        <v>	(12, 'ITA'),</v>
       </c>
     </row>
     <row r="15" spans="7:10">
@@ -14374,7 +14441,7 @@
       </c>
       <c r="J15" t="str">
         <f t="shared" si="0"/>
-        <v>(13, 'COL'),</v>
+        <v>	(13, 'COL'),</v>
       </c>
     </row>
     <row r="16" spans="7:10">
@@ -14389,7 +14456,7 @@
       </c>
       <c r="J16" t="str">
         <f t="shared" si="0"/>
-        <v>(14, 'MEX'),</v>
+        <v>	(14, 'MEX'),</v>
       </c>
     </row>
     <row r="17" spans="7:10">
@@ -14404,7 +14471,7 @@
       </c>
       <c r="J17" t="str">
         <f t="shared" si="0"/>
-        <v>(15, 'SEN'),</v>
+        <v>	(15, 'SEN'),</v>
       </c>
     </row>
     <row r="18" spans="7:10">
@@ -14419,7 +14486,7 @@
       </c>
       <c r="J18" t="str">
         <f t="shared" si="0"/>
-        <v>(16, 'URU'),</v>
+        <v>	(16, 'URU'),</v>
       </c>
     </row>
     <row r="19" spans="7:10">
@@ -14434,7 +14501,7 @@
       </c>
       <c r="J19" t="str">
         <f t="shared" si="0"/>
-        <v>(17, 'USA'),</v>
+        <v>	(17, 'USA'),</v>
       </c>
     </row>
     <row r="20" spans="7:10">
@@ -14449,7 +14516,7 @@
       </c>
       <c r="J20" t="str">
         <f t="shared" si="0"/>
-        <v>(18, 'JPN'),</v>
+        <v>	(18, 'JPN'),</v>
       </c>
     </row>
     <row r="21" spans="7:10">
@@ -14464,7 +14531,7 @@
       </c>
       <c r="J21" t="str">
         <f t="shared" si="0"/>
-        <v>(19, 'SUI'),</v>
+        <v>	(19, 'SUI'),</v>
       </c>
     </row>
     <row r="22" spans="7:10">
@@ -14479,7 +14546,7 @@
       </c>
       <c r="J22" t="str">
         <f t="shared" si="0"/>
-        <v>(20, 'IRN'),</v>
+        <v>	(20, 'IRN'),</v>
       </c>
     </row>
     <row r="23" spans="7:10">
@@ -14494,7 +14561,7 @@
       </c>
       <c r="J23" t="str">
         <f t="shared" si="0"/>
-        <v>(21, 'DEN'),</v>
+        <v>	(21, 'DEN'),</v>
       </c>
     </row>
     <row r="24" spans="7:10">
@@ -14509,7 +14576,7 @@
       </c>
       <c r="J24" t="str">
         <f t="shared" si="0"/>
-        <v>(22, 'TUR'),</v>
+        <v>	(22, 'TUR'),</v>
       </c>
     </row>
     <row r="25" spans="7:10">
@@ -14524,7 +14591,7 @@
       </c>
       <c r="J25" t="str">
         <f t="shared" si="0"/>
-        <v>(23, 'ECU'),</v>
+        <v>	(23, 'ECU'),</v>
       </c>
     </row>
     <row r="26" spans="7:10">
@@ -14539,7 +14606,7 @@
       </c>
       <c r="J26" t="str">
         <f t="shared" si="0"/>
-        <v>(24, 'AUT'),</v>
+        <v>	(24, 'AUT'),</v>
       </c>
     </row>
     <row r="27" spans="7:10">
@@ -14554,7 +14621,7 @@
       </c>
       <c r="J27" t="str">
         <f t="shared" si="0"/>
-        <v>(25, 'KOR'),</v>
+        <v>	(25, 'KOR'),</v>
       </c>
     </row>
     <row r="28" spans="7:10">
@@ -14569,7 +14636,7 @@
       </c>
       <c r="J28" t="str">
         <f t="shared" si="0"/>
-        <v>(26, 'NGA'),</v>
+        <v>	(26, 'NGA'),</v>
       </c>
     </row>
     <row r="29" spans="7:10">
@@ -14584,7 +14651,7 @@
       </c>
       <c r="J29" t="str">
         <f t="shared" si="0"/>
-        <v>(27, 'AUS'),</v>
+        <v>	(27, 'AUS'),</v>
       </c>
     </row>
     <row r="30" spans="7:10">
@@ -14599,7 +14666,7 @@
       </c>
       <c r="J30" t="str">
         <f t="shared" si="0"/>
-        <v>(28, 'ALG'),</v>
+        <v>	(28, 'ALG'),</v>
       </c>
     </row>
     <row r="31" spans="7:10">
@@ -14614,7 +14681,7 @@
       </c>
       <c r="J31" t="str">
         <f t="shared" si="0"/>
-        <v>(29, 'EGY'),</v>
+        <v>	(29, 'EGY'),</v>
       </c>
     </row>
     <row r="32" spans="7:10">
@@ -14629,7 +14696,7 @@
       </c>
       <c r="J32" t="str">
         <f t="shared" si="0"/>
-        <v>(30, 'CAN'),</v>
+        <v>	(30, 'CAN'),</v>
       </c>
     </row>
     <row r="33" spans="7:10">
@@ -14644,7 +14711,7 @@
       </c>
       <c r="J33" t="str">
         <f t="shared" si="0"/>
-        <v>(31, 'NOR'),</v>
+        <v>	(31, 'NOR'),</v>
       </c>
     </row>
     <row r="34" spans="7:10">
@@ -14659,7 +14726,7 @@
       </c>
       <c r="J34" t="str">
         <f t="shared" si="0"/>
-        <v>(32, 'UKR'),</v>
+        <v>	(32, 'UKR'),</v>
       </c>
     </row>
     <row r="35" spans="7:10">
@@ -14674,7 +14741,7 @@
       </c>
       <c r="J35" t="str">
         <f t="shared" si="0"/>
-        <v>(33, 'CIV'),</v>
+        <v>	(33, 'CIV'),</v>
       </c>
     </row>
     <row r="36" spans="7:10">
@@ -14689,7 +14756,7 @@
       </c>
       <c r="J36" t="str">
         <f t="shared" si="0"/>
-        <v>(34, 'PAN'),</v>
+        <v>	(34, 'PAN'),</v>
       </c>
     </row>
     <row r="37" spans="7:10">
@@ -14704,7 +14771,7 @@
       </c>
       <c r="J37" t="str">
         <f t="shared" si="0"/>
-        <v>(35, 'RUS'),</v>
+        <v>	(35, 'RUS'),</v>
       </c>
     </row>
     <row r="38" spans="7:10">
@@ -14719,7 +14786,7 @@
       </c>
       <c r="J38" t="str">
         <f t="shared" si="0"/>
-        <v>(36, 'POL'),</v>
+        <v>	(36, 'POL'),</v>
       </c>
     </row>
     <row r="39" spans="7:10">
@@ -14734,7 +14801,7 @@
       </c>
       <c r="J39" t="str">
         <f t="shared" si="0"/>
-        <v>(37, 'WAL'),</v>
+        <v>	(37, 'WAL'),</v>
       </c>
     </row>
     <row r="40" spans="7:10">
@@ -14749,7 +14816,7 @@
       </c>
       <c r="J40" t="str">
         <f t="shared" si="0"/>
-        <v>(38, 'SWE'),</v>
+        <v>	(38, 'SWE'),</v>
       </c>
     </row>
     <row r="41" spans="7:10">
@@ -14764,7 +14831,7 @@
       </c>
       <c r="J41" t="str">
         <f t="shared" si="0"/>
-        <v>(39, 'HUN'),</v>
+        <v>	(39, 'HUN'),</v>
       </c>
     </row>
     <row r="42" spans="7:10">
@@ -14779,7 +14846,7 @@
       </c>
       <c r="J42" t="str">
         <f t="shared" si="0"/>
-        <v>(40, 'CZE'),</v>
+        <v>	(40, 'CZE'),</v>
       </c>
     </row>
     <row r="43" spans="7:10">
@@ -14794,7 +14861,7 @@
       </c>
       <c r="J43" t="str">
         <f t="shared" si="0"/>
-        <v>(41, 'PAR'),</v>
+        <v>	(41, 'PAR'),</v>
       </c>
     </row>
     <row r="44" spans="7:10">
@@ -14809,7 +14876,7 @@
       </c>
       <c r="J44" t="str">
         <f t="shared" si="0"/>
-        <v>(42, 'SCO'),</v>
+        <v>	(42, 'SCO'),</v>
       </c>
     </row>
     <row r="45" spans="7:10">
@@ -14824,7 +14891,7 @@
       </c>
       <c r="J45" t="str">
         <f t="shared" si="0"/>
-        <v>(43, 'SRB'),</v>
+        <v>	(43, 'SRB'),</v>
       </c>
     </row>
     <row r="46" spans="7:10">
@@ -14839,7 +14906,7 @@
       </c>
       <c r="J46" t="str">
         <f t="shared" si="0"/>
-        <v>(44, 'CMR'),</v>
+        <v>	(44, 'CMR'),</v>
       </c>
     </row>
     <row r="47" spans="7:10">
@@ -14854,7 +14921,7 @@
       </c>
       <c r="J47" t="str">
         <f t="shared" si="0"/>
-        <v>(45, 'TUN'),</v>
+        <v>	(45, 'TUN'),</v>
       </c>
     </row>
     <row r="48" spans="7:10">
@@ -14869,7 +14936,7 @@
       </c>
       <c r="J48" t="str">
         <f t="shared" si="0"/>
-        <v>(46, 'COD'),</v>
+        <v>	(46, 'COD'),</v>
       </c>
     </row>
     <row r="49" spans="7:10">
@@ -14884,7 +14951,7 @@
       </c>
       <c r="J49" t="str">
         <f t="shared" si="0"/>
-        <v>(47, 'SVK'),</v>
+        <v>	(47, 'SVK'),</v>
       </c>
     </row>
     <row r="50" spans="7:10">
@@ -14899,7 +14966,7 @@
       </c>
       <c r="J50" t="str">
         <f t="shared" si="0"/>
-        <v>(48, 'GRE'),</v>
+        <v>	(48, 'GRE'),</v>
       </c>
     </row>
     <row r="51" spans="7:10">
@@ -14914,7 +14981,7 @@
       </c>
       <c r="J51" t="str">
         <f t="shared" si="0"/>
-        <v>(49, 'VEN'),</v>
+        <v>	(49, 'VEN'),</v>
       </c>
     </row>
     <row r="52" spans="7:10">
@@ -14929,7 +14996,7 @@
       </c>
       <c r="J52" t="str">
         <f t="shared" si="0"/>
-        <v>(50, 'UZB'),</v>
+        <v>	(50, 'UZB'),</v>
       </c>
     </row>
     <row r="53" spans="7:10">
@@ -14944,7 +15011,7 @@
       </c>
       <c r="J53" t="str">
         <f t="shared" si="0"/>
-        <v>(51, 'CHI'),</v>
+        <v>	(51, 'CHI'),</v>
       </c>
     </row>
     <row r="54" spans="7:10">
@@ -14959,7 +15026,7 @@
       </c>
       <c r="J54" t="str">
         <f t="shared" si="0"/>
-        <v>(52, 'PER'),</v>
+        <v>	(52, 'PER'),</v>
       </c>
     </row>
     <row r="55" spans="7:10">
@@ -14974,7 +15041,7 @@
       </c>
       <c r="J55" t="str">
         <f t="shared" si="0"/>
-        <v>(53, 'CRC'),</v>
+        <v>	(53, 'CRC'),</v>
       </c>
     </row>
     <row r="56" spans="7:10">
@@ -14989,7 +15056,7 @@
       </c>
       <c r="J56" t="str">
         <f t="shared" si="0"/>
-        <v>(54, 'ROU'),</v>
+        <v>	(54, 'ROU'),</v>
       </c>
     </row>
     <row r="57" spans="7:10">
@@ -15004,7 +15071,7 @@
       </c>
       <c r="J57" t="str">
         <f t="shared" si="0"/>
-        <v>(55, 'MLI'),</v>
+        <v>	(55, 'MLI'),</v>
       </c>
     </row>
     <row r="58" spans="7:10">
@@ -15019,7 +15086,7 @@
       </c>
       <c r="J58" t="str">
         <f t="shared" si="0"/>
-        <v>(56, 'QAT'),</v>
+        <v>	(56, 'QAT'),</v>
       </c>
     </row>
     <row r="59" spans="7:10">
@@ -15034,7 +15101,7 @@
       </c>
       <c r="J59" t="str">
         <f t="shared" si="0"/>
-        <v>(57, 'IRQ'),</v>
+        <v>	(57, 'IRQ'),</v>
       </c>
     </row>
     <row r="60" spans="7:10">
@@ -15049,7 +15116,7 @@
       </c>
       <c r="J60" t="str">
         <f t="shared" si="0"/>
-        <v>(58, 'IRL'),</v>
+        <v>	(58, 'IRL'),</v>
       </c>
     </row>
     <row r="61" spans="7:10">
@@ -15064,7 +15131,7 @@
       </c>
       <c r="J61" t="str">
         <f t="shared" si="0"/>
-        <v>(59, 'SVN'),</v>
+        <v>	(59, 'SVN'),</v>
       </c>
     </row>
     <row r="62" spans="7:10">
@@ -15079,7 +15146,7 @@
       </c>
       <c r="J62" t="str">
         <f t="shared" si="0"/>
-        <v>(60, 'RSA'),</v>
+        <v>	(60, 'RSA'),</v>
       </c>
     </row>
     <row r="63" spans="7:10">
@@ -15094,7 +15161,7 @@
       </c>
       <c r="J63" t="str">
         <f t="shared" si="0"/>
-        <v>(61, 'KSA'),</v>
+        <v>	(61, 'KSA'),</v>
       </c>
     </row>
     <row r="64" spans="7:10">
@@ -15109,7 +15176,7 @@
       </c>
       <c r="J64" t="str">
         <f t="shared" si="0"/>
-        <v>(62, 'BFA'),</v>
+        <v>	(62, 'BFA'),</v>
       </c>
     </row>
     <row r="65" spans="7:10">
@@ -15124,7 +15191,7 @@
       </c>
       <c r="J65" t="str">
         <f t="shared" si="0"/>
-        <v>(63, 'JOR'),</v>
+        <v>	(63, 'JOR'),</v>
       </c>
     </row>
     <row r="66" spans="7:10">
@@ -15139,7 +15206,7 @@
       </c>
       <c r="J66" t="str">
         <f t="shared" si="0"/>
-        <v>(64, 'BIH'),</v>
+        <v>	(64, 'BIH'),</v>
       </c>
     </row>
     <row r="67" spans="7:10">
@@ -15153,8 +15220,8 @@
         <v>486</v>
       </c>
       <c r="J67" t="str">
-        <f t="shared" ref="J67:J130" si="1">CHAR(9)&amp;"("&amp;G67&amp;", '"&amp;H67&amp;"'), "</f>
-        <v>(65, 'HON'),</v>
+        <f t="shared" ref="J67:J130" si="1">CHAR(9)&amp;"("&amp;G67&amp;", '"&amp;H67&amp;"'),"</f>
+        <v>	(65, 'HON'),</v>
       </c>
     </row>
     <row r="68" spans="7:10">
@@ -15169,7 +15236,7 @@
       </c>
       <c r="J68" t="str">
         <f t="shared" si="1"/>
-        <v>(66, 'ALB'),</v>
+        <v>	(66, 'ALB'),</v>
       </c>
     </row>
     <row r="69" spans="7:10">
@@ -15184,7 +15251,7 @@
       </c>
       <c r="J69" t="str">
         <f t="shared" si="1"/>
-        <v>(67, 'CPV'),</v>
+        <v>	(67, 'CPV'),</v>
       </c>
     </row>
     <row r="70" spans="7:10">
@@ -15199,7 +15266,7 @@
       </c>
       <c r="J70" t="str">
         <f t="shared" si="1"/>
-        <v>(68, 'UAE'),</v>
+        <v>	(68, 'UAE'),</v>
       </c>
     </row>
     <row r="71" spans="7:10">
@@ -15214,7 +15281,7 @@
       </c>
       <c r="J71" t="str">
         <f t="shared" si="1"/>
-        <v>(69, 'MKD'),</v>
+        <v>	(69, 'MKD'),</v>
       </c>
     </row>
     <row r="72" spans="7:10">
@@ -15229,7 +15296,7 @@
       </c>
       <c r="J72" t="str">
         <f t="shared" si="1"/>
-        <v>(70, 'NIR'),</v>
+        <v>	(70, 'NIR'),</v>
       </c>
     </row>
     <row r="73" spans="7:10">
@@ -15244,7 +15311,7 @@
       </c>
       <c r="J73" t="str">
         <f t="shared" si="1"/>
-        <v>(71, 'JAM'),</v>
+        <v>	(71, 'JAM'),</v>
       </c>
     </row>
     <row r="74" spans="7:10">
@@ -15259,7 +15326,7 @@
       </c>
       <c r="J74" t="str">
         <f t="shared" si="1"/>
-        <v>(72, 'GEO'),</v>
+        <v>	(72, 'GEO'),</v>
       </c>
     </row>
     <row r="75" spans="7:10">
@@ -15274,7 +15341,7 @@
       </c>
       <c r="J75" t="str">
         <f t="shared" si="1"/>
-        <v>(73, 'GHA'),</v>
+        <v>	(73, 'GHA'),</v>
       </c>
     </row>
     <row r="76" spans="7:10">
@@ -15289,7 +15356,7 @@
       </c>
       <c r="J76" t="str">
         <f t="shared" si="1"/>
-        <v>(74, 'ISL'),</v>
+        <v>	(74, 'ISL'),</v>
       </c>
     </row>
     <row r="77" spans="7:10">
@@ -15304,7 +15371,7 @@
       </c>
       <c r="J77" t="str">
         <f t="shared" si="1"/>
-        <v>(75, 'FIN'),</v>
+        <v>	(75, 'FIN'),</v>
       </c>
     </row>
     <row r="78" spans="7:10">
@@ -15319,7 +15386,7 @@
       </c>
       <c r="J78" t="str">
         <f t="shared" si="1"/>
-        <v>(76, 'ISR'),</v>
+        <v>	(76, 'ISR'),</v>
       </c>
     </row>
     <row r="79" spans="7:10">
@@ -15334,7 +15401,7 @@
       </c>
       <c r="J79" t="str">
         <f t="shared" si="1"/>
-        <v>(77, 'BOL'),</v>
+        <v>	(77, 'BOL'),</v>
       </c>
     </row>
     <row r="80" spans="7:10">
@@ -15349,7 +15416,7 @@
       </c>
       <c r="J80" t="str">
         <f t="shared" si="1"/>
-        <v>(78, 'KOS'),</v>
+        <v>	(78, 'KOS'),</v>
       </c>
     </row>
     <row r="81" spans="7:10">
@@ -15364,7 +15431,7 @@
       </c>
       <c r="J81" t="str">
         <f t="shared" si="1"/>
-        <v>(79, 'OMA'),</v>
+        <v>	(79, 'OMA'),</v>
       </c>
     </row>
     <row r="82" spans="7:10">
@@ -15379,7 +15446,7 @@
       </c>
       <c r="J82" t="str">
         <f t="shared" si="1"/>
-        <v>(80, 'MNE'),</v>
+        <v>	(80, 'MNE'),</v>
       </c>
     </row>
     <row r="83" spans="7:10">
@@ -15394,7 +15461,7 @@
       </c>
       <c r="J83" t="str">
         <f t="shared" si="1"/>
-        <v>(81, 'GUI'),</v>
+        <v>	(81, 'GUI'),</v>
       </c>
     </row>
     <row r="84" spans="7:10">
@@ -15409,7 +15476,7 @@
       </c>
       <c r="J84" t="str">
         <f t="shared" si="1"/>
-        <v>(82, 'CUW'),</v>
+        <v>	(82, 'CUW'),</v>
       </c>
     </row>
     <row r="85" spans="7:10">
@@ -15424,7 +15491,7 @@
       </c>
       <c r="J85" t="str">
         <f t="shared" si="1"/>
-        <v>(83, 'HAI'),</v>
+        <v>	(83, 'HAI'),</v>
       </c>
     </row>
     <row r="86" spans="7:10">
@@ -15439,7 +15506,7 @@
       </c>
       <c r="J86" t="str">
         <f t="shared" si="1"/>
-        <v>(84, 'SYR'),</v>
+        <v>	(84, 'SYR'),</v>
       </c>
     </row>
     <row r="87" spans="7:10">
@@ -15454,7 +15521,7 @@
       </c>
       <c r="J87" t="str">
         <f t="shared" si="1"/>
-        <v>(85, 'NZL'),</v>
+        <v>	(85, 'NZL'),</v>
       </c>
     </row>
     <row r="88" spans="7:10">
@@ -15469,7 +15536,7 @@
       </c>
       <c r="J88" t="str">
         <f t="shared" si="1"/>
-        <v>(86, 'GAB'),</v>
+        <v>	(86, 'GAB'),</v>
       </c>
     </row>
     <row r="89" spans="7:10">
@@ -15484,7 +15551,7 @@
       </c>
       <c r="J89" t="str">
         <f t="shared" si="1"/>
-        <v>(87, 'BUL'),</v>
+        <v>	(87, 'BUL'),</v>
       </c>
     </row>
     <row r="90" spans="7:10">
@@ -15499,7 +15566,7 @@
       </c>
       <c r="J90" t="str">
         <f t="shared" si="1"/>
-        <v>(88, 'ANG'),</v>
+        <v>	(88, 'ANG'),</v>
       </c>
     </row>
     <row r="91" spans="7:10">
@@ -15514,7 +15581,7 @@
       </c>
       <c r="J91" t="str">
         <f t="shared" si="1"/>
-        <v>(89, 'UGA'),</v>
+        <v>	(89, 'UGA'),</v>
       </c>
     </row>
     <row r="92" spans="7:10">
@@ -15529,7 +15596,7 @@
       </c>
       <c r="J92" t="str">
         <f t="shared" si="1"/>
-        <v>(90, 'ZAM'),</v>
+        <v>	(90, 'ZAM'),</v>
       </c>
     </row>
     <row r="93" spans="7:10">
@@ -15544,7 +15611,7 @@
       </c>
       <c r="J93" t="str">
         <f t="shared" si="1"/>
-        <v>(91, 'CHN'),</v>
+        <v>	(91, 'CHN'),</v>
       </c>
     </row>
     <row r="94" spans="7:10">
@@ -15559,7 +15626,7 @@
       </c>
       <c r="J94" t="str">
         <f t="shared" si="1"/>
-        <v>(92, 'BHR'),</v>
+        <v>	(92, 'BHR'),</v>
       </c>
     </row>
     <row r="95" spans="7:10">
@@ -15574,7 +15641,7 @@
       </c>
       <c r="J95" t="str">
         <f t="shared" si="1"/>
-        <v>(93, 'BEN'),</v>
+        <v>	(93, 'BEN'),</v>
       </c>
     </row>
     <row r="96" spans="7:10">
@@ -15589,7 +15656,7 @@
       </c>
       <c r="J96" t="str">
         <f t="shared" si="1"/>
-        <v>(94, 'THA'),</v>
+        <v>	(94, 'THA'),</v>
       </c>
     </row>
     <row r="97" spans="7:10">
@@ -15604,7 +15671,7 @@
       </c>
       <c r="J97" t="str">
         <f t="shared" si="1"/>
-        <v>(95, 'PSE'),</v>
+        <v>	(95, 'PSE'),</v>
       </c>
     </row>
     <row r="98" spans="7:10">
@@ -15619,7 +15686,7 @@
       </c>
       <c r="J98" t="str">
         <f t="shared" si="1"/>
-        <v>(96, 'BLR'),</v>
+        <v>	(96, 'BLR'),</v>
       </c>
     </row>
     <row r="99" spans="7:10">
@@ -15634,7 +15701,7 @@
       </c>
       <c r="J99" t="str">
         <f t="shared" si="1"/>
-        <v>(97, 'GUA'),</v>
+        <v>	(97, 'GUA'),</v>
       </c>
     </row>
     <row r="100" spans="7:10">
@@ -15649,7 +15716,7 @@
       </c>
       <c r="J100" t="str">
         <f t="shared" si="1"/>
-        <v>(98, 'LUX'),</v>
+        <v>	(98, 'LUX'),</v>
       </c>
     </row>
     <row r="101" spans="7:10">
@@ -15664,7 +15731,7 @@
       </c>
       <c r="J101" t="str">
         <f t="shared" si="1"/>
-        <v>(99, 'VIE'),</v>
+        <v>	(99, 'VIE'),</v>
       </c>
     </row>
     <row r="102" spans="7:10">
@@ -15679,7 +15746,7 @@
       </c>
       <c r="J102" t="str">
         <f t="shared" si="1"/>
-        <v>(100, 'SLV'),</v>
+        <v>	(100, 'SLV'),</v>
       </c>
     </row>
     <row r="103" spans="7:10">
@@ -15694,7 +15761,7 @@
       </c>
       <c r="J103" t="str">
         <f t="shared" si="1"/>
-        <v>(101, 'TJK'),</v>
+        <v>	(101, 'TJK'),</v>
       </c>
     </row>
     <row r="104" spans="7:10">
@@ -15709,7 +15776,7 @@
       </c>
       <c r="J104" t="str">
         <f t="shared" si="1"/>
-        <v>(102, 'TRI'),</v>
+        <v>	(102, 'TRI'),</v>
       </c>
     </row>
     <row r="105" spans="7:10">
@@ -15724,7 +15791,7 @@
       </c>
       <c r="J105" t="str">
         <f t="shared" si="1"/>
-        <v>(103, 'MOZ'),</v>
+        <v>	(103, 'MOZ'),</v>
       </c>
     </row>
     <row r="106" spans="7:10">
@@ -15739,7 +15806,7 @@
       </c>
       <c r="J106" t="str">
         <f t="shared" si="1"/>
-        <v>(104, 'MAD'),</v>
+        <v>	(104, 'MAD'),</v>
       </c>
     </row>
     <row r="107" spans="7:10">
@@ -15754,7 +15821,7 @@
       </c>
       <c r="J107" t="str">
         <f t="shared" si="1"/>
-        <v>(105, 'EQG'),</v>
+        <v>	(105, 'EQG'),</v>
       </c>
     </row>
     <row r="108" spans="7:10">
@@ -15769,7 +15836,7 @@
       </c>
       <c r="J108" t="str">
         <f t="shared" si="1"/>
-        <v>(106, 'KGZ'),</v>
+        <v>	(106, 'KGZ'),</v>
       </c>
     </row>
     <row r="109" spans="7:10">
@@ -15784,7 +15851,7 @@
       </c>
       <c r="J109" t="str">
         <f t="shared" si="1"/>
-        <v>(107, 'ARM'),</v>
+        <v>	(107, 'ARM'),</v>
       </c>
     </row>
     <row r="110" spans="7:10">
@@ -15799,7 +15866,7 @@
       </c>
       <c r="J110" t="str">
         <f t="shared" si="1"/>
-        <v>(108, 'COM'),</v>
+        <v>	(108, 'COM'),</v>
       </c>
     </row>
     <row r="111" spans="7:10">
@@ -15814,7 +15881,7 @@
       </c>
       <c r="J111" t="str">
         <f t="shared" si="1"/>
-        <v>(109, 'KEN'),</v>
+        <v>	(109, 'KEN'),</v>
       </c>
     </row>
     <row r="112" spans="7:10">
@@ -15829,7 +15896,7 @@
       </c>
       <c r="J112" t="str">
         <f t="shared" si="1"/>
-        <v>(110, 'LBY'),</v>
+        <v>	(110, 'LBY'),</v>
       </c>
     </row>
     <row r="113" spans="7:10">
@@ -15844,7 +15911,7 @@
       </c>
       <c r="J113" t="str">
         <f t="shared" si="1"/>
-        <v>(111, 'KAZ'),</v>
+        <v>	(111, 'KAZ'),</v>
       </c>
     </row>
     <row r="114" spans="7:10">
@@ -15859,7 +15926,7 @@
       </c>
       <c r="J114" t="str">
         <f t="shared" si="1"/>
-        <v>(112, 'TAN'),</v>
+        <v>	(112, 'TAN'),</v>
       </c>
     </row>
     <row r="115" spans="7:10">
@@ -15874,7 +15941,7 @@
       </c>
       <c r="J115" t="str">
         <f t="shared" si="1"/>
-        <v>(113, 'MTN'),</v>
+        <v>	(113, 'MTN'),</v>
       </c>
     </row>
     <row r="116" spans="7:10">
@@ -15889,7 +15956,7 @@
       </c>
       <c r="J116" t="str">
         <f t="shared" si="1"/>
-        <v>(114, 'NER'),</v>
+        <v>	(114, 'NER'),</v>
       </c>
     </row>
     <row r="117" spans="7:10">
@@ -15904,7 +15971,7 @@
       </c>
       <c r="J117" t="str">
         <f t="shared" si="1"/>
-        <v>(115, 'LBN'),</v>
+        <v>	(115, 'LBN'),</v>
       </c>
     </row>
     <row r="118" spans="7:10">
@@ -15919,7 +15986,7 @@
       </c>
       <c r="J118" t="str">
         <f t="shared" si="1"/>
-        <v>(116, 'GAM'),</v>
+        <v>	(116, 'GAM'),</v>
       </c>
     </row>
     <row r="119" spans="7:10">
@@ -15934,7 +16001,7 @@
       </c>
       <c r="J119" t="str">
         <f t="shared" si="1"/>
-        <v>(117, 'SDN'),</v>
+        <v>	(117, 'SDN'),</v>
       </c>
     </row>
     <row r="120" spans="7:10">
@@ -15949,7 +16016,7 @@
       </c>
       <c r="J120" t="str">
         <f t="shared" si="1"/>
-        <v>(118, 'IDN'),</v>
+        <v>	(118, 'IDN'),</v>
       </c>
     </row>
     <row r="121" spans="7:10">
@@ -15964,7 +16031,7 @@
       </c>
       <c r="J121" t="str">
         <f t="shared" si="1"/>
-        <v>(119, 'TOG'),</v>
+        <v>	(119, 'TOG'),</v>
       </c>
     </row>
     <row r="122" spans="7:10">
@@ -15979,7 +16046,7 @@
       </c>
       <c r="J122" t="str">
         <f t="shared" si="1"/>
-        <v>(120, 'PRK'),</v>
+        <v>	(120, 'PRK'),</v>
       </c>
     </row>
     <row r="123" spans="7:10">
@@ -15994,7 +16061,7 @@
       </c>
       <c r="J123" t="str">
         <f t="shared" si="1"/>
-        <v>(121, 'NAM'),</v>
+        <v>	(121, 'NAM'),</v>
       </c>
     </row>
     <row r="124" spans="7:10">
@@ -16009,7 +16076,7 @@
       </c>
       <c r="J124" t="str">
         <f t="shared" si="1"/>
-        <v>(122, 'SLE'),</v>
+        <v>	(122, 'SLE'),</v>
       </c>
     </row>
     <row r="125" spans="7:10">
@@ -16024,7 +16091,7 @@
       </c>
       <c r="J125" t="str">
         <f t="shared" si="1"/>
-        <v>(123, 'FRO'),</v>
+        <v>	(123, 'FRO'),</v>
       </c>
     </row>
     <row r="126" spans="7:10">
@@ -16039,7 +16106,7 @@
       </c>
       <c r="J126" t="str">
         <f t="shared" si="1"/>
-        <v>(124, 'CYP'),</v>
+        <v>	(124, 'CYP'),</v>
       </c>
     </row>
     <row r="127" spans="7:10">
@@ -16054,7 +16121,7 @@
       </c>
       <c r="J127" t="str">
         <f t="shared" si="1"/>
-        <v>(125, 'SUR'),</v>
+        <v>	(125, 'SUR'),</v>
       </c>
     </row>
     <row r="128" spans="7:10">
@@ -16069,7 +16136,7 @@
       </c>
       <c r="J128" t="str">
         <f t="shared" si="1"/>
-        <v>(126, 'AZE'),</v>
+        <v>	(126, 'AZE'),</v>
       </c>
     </row>
     <row r="129" spans="7:10">
@@ -16084,7 +16151,7 @@
       </c>
       <c r="J129" t="str">
         <f t="shared" si="1"/>
-        <v>(127, 'EST'),</v>
+        <v>	(127, 'EST'),</v>
       </c>
     </row>
     <row r="130" spans="7:10">
@@ -16099,7 +16166,7 @@
       </c>
       <c r="J130" t="str">
         <f t="shared" si="1"/>
-        <v>(128, 'RWA'),</v>
+        <v>	(128, 'RWA'),</v>
       </c>
     </row>
     <row r="131" spans="7:10">
@@ -16113,8 +16180,8 @@
         <v>604</v>
       </c>
       <c r="J131" t="str">
-        <f t="shared" ref="J131:J194" si="2">CHAR(9)&amp;"("&amp;G131&amp;", '"&amp;H131&amp;"'), "</f>
-        <v>(129, 'MWI'),</v>
+        <f t="shared" ref="J131:J194" si="2">CHAR(9)&amp;"("&amp;G131&amp;", '"&amp;H131&amp;"'),"</f>
+        <v>	(129, 'MWI'),</v>
       </c>
     </row>
     <row r="132" spans="7:10">
@@ -16129,7 +16196,7 @@
       </c>
       <c r="J132" t="str">
         <f t="shared" si="2"/>
-        <v>(130, 'ZIM'),</v>
+        <v>	(130, 'ZIM'),</v>
       </c>
     </row>
     <row r="133" spans="7:10">
@@ -16144,7 +16211,7 @@
       </c>
       <c r="J133" t="str">
         <f t="shared" si="2"/>
-        <v>(131, 'NCA'),</v>
+        <v>	(131, 'NCA'),</v>
       </c>
     </row>
     <row r="134" spans="7:10">
@@ -16159,7 +16226,7 @@
       </c>
       <c r="J134" t="str">
         <f t="shared" si="2"/>
-        <v>(132, 'GNB'),</v>
+        <v>	(132, 'GNB'),</v>
       </c>
     </row>
     <row r="135" spans="7:10">
@@ -16174,7 +16241,7 @@
       </c>
       <c r="J135" t="str">
         <f t="shared" si="2"/>
-        <v>(133, 'KUW'),</v>
+        <v>	(133, 'KUW'),</v>
       </c>
     </row>
     <row r="136" spans="7:10">
@@ -16189,7 +16256,7 @@
       </c>
       <c r="J136" t="str">
         <f t="shared" si="2"/>
-        <v>(134, 'CGO'),</v>
+        <v>	(134, 'CGO'),</v>
       </c>
     </row>
     <row r="137" spans="7:10">
@@ -16204,7 +16271,7 @@
       </c>
       <c r="J137" t="str">
         <f t="shared" si="2"/>
-        <v>(135, 'PHI'),</v>
+        <v>	(135, 'PHI'),</v>
       </c>
     </row>
     <row r="138" spans="7:10">
@@ -16219,7 +16286,7 @@
       </c>
       <c r="J138" t="str">
         <f t="shared" si="2"/>
-        <v>(136, 'MAS'),</v>
+        <v>	(136, 'MAS'),</v>
       </c>
     </row>
     <row r="139" spans="7:10">
@@ -16234,7 +16301,7 @@
       </c>
       <c r="J139" t="str">
         <f t="shared" si="2"/>
-        <v>(137, 'LVA'),</v>
+        <v>	(137, 'LVA'),</v>
       </c>
     </row>
     <row r="140" spans="7:10">
@@ -16249,7 +16316,7 @@
       </c>
       <c r="J140" t="str">
         <f t="shared" si="2"/>
-        <v>(138, 'IND'),</v>
+        <v>	(138, 'IND'),</v>
       </c>
     </row>
     <row r="141" spans="7:10">
@@ -16264,7 +16331,7 @@
       </c>
       <c r="J141" t="str">
         <f t="shared" si="2"/>
-        <v>(139, 'CTA'),</v>
+        <v>	(139, 'CTA'),</v>
       </c>
     </row>
     <row r="142" spans="7:10">
@@ -16279,7 +16346,7 @@
       </c>
       <c r="J142" t="str">
         <f t="shared" si="2"/>
-        <v>(140, 'LBR'),</v>
+        <v>	(140, 'LBR'),</v>
       </c>
     </row>
     <row r="143" spans="7:10">
@@ -16294,7 +16361,7 @@
       </c>
       <c r="J143" t="str">
         <f t="shared" si="2"/>
-        <v>(141, 'TKM'),</v>
+        <v>	(141, 'TKM'),</v>
       </c>
     </row>
     <row r="144" spans="7:10">
@@ -16309,7 +16376,7 @@
       </c>
       <c r="J144" t="str">
         <f t="shared" si="2"/>
-        <v>(142, 'BDI'),</v>
+        <v>	(142, 'BDI'),</v>
       </c>
     </row>
     <row r="145" spans="7:10">
@@ -16324,7 +16391,7 @@
       </c>
       <c r="J145" t="str">
         <f t="shared" si="2"/>
-        <v>(143, 'ETH'),</v>
+        <v>	(143, 'ETH'),</v>
       </c>
     </row>
     <row r="146" spans="7:10">
@@ -16339,7 +16406,7 @@
       </c>
       <c r="J146" t="str">
         <f t="shared" si="2"/>
-        <v>(144, 'DOM'),</v>
+        <v>	(144, 'DOM'),</v>
       </c>
     </row>
     <row r="147" spans="7:10">
@@ -16354,7 +16421,7 @@
       </c>
       <c r="J147" t="str">
         <f t="shared" si="2"/>
-        <v>(145, 'YEM'),</v>
+        <v>	(145, 'YEM'),</v>
       </c>
     </row>
     <row r="148" spans="7:10">
@@ -16369,7 +16436,7 @@
       </c>
       <c r="J148" t="str">
         <f t="shared" si="2"/>
-        <v>(146, 'LES'),</v>
+        <v>	(146, 'LES'),</v>
       </c>
     </row>
     <row r="149" spans="7:10">
@@ -16384,7 +16451,7 @@
       </c>
       <c r="J149" t="str">
         <f t="shared" si="2"/>
-        <v>(147, 'BOT'),</v>
+        <v>	(147, 'BOT'),</v>
       </c>
     </row>
     <row r="150" spans="7:10">
@@ -16399,7 +16466,7 @@
       </c>
       <c r="J150" t="str">
         <f t="shared" si="2"/>
-        <v>(148, 'SIN'),</v>
+        <v>	(148, 'SIN'),</v>
       </c>
     </row>
     <row r="151" spans="7:10">
@@ -16414,7 +16481,7 @@
       </c>
       <c r="J151" t="str">
         <f t="shared" si="2"/>
-        <v>(149, 'LTU'),</v>
+        <v>	(149, 'LTU'),</v>
       </c>
     </row>
     <row r="152" spans="7:10">
@@ -16429,7 +16496,7 @@
       </c>
       <c r="J152" t="str">
         <f t="shared" si="2"/>
-        <v>(150, 'GUY'),</v>
+        <v>	(150, 'GUY'),</v>
       </c>
     </row>
     <row r="153" spans="7:10">
@@ -16444,7 +16511,7 @@
       </c>
       <c r="J153" t="str">
         <f t="shared" si="2"/>
-        <v>(151, 'NCL'),</v>
+        <v>	(151, 'NCL'),</v>
       </c>
     </row>
     <row r="154" spans="7:10">
@@ -16459,7 +16526,7 @@
       </c>
       <c r="J154" t="str">
         <f t="shared" si="2"/>
-        <v>(152, 'KNA'),</v>
+        <v>	(152, 'KNA'),</v>
       </c>
     </row>
     <row r="155" spans="7:10">
@@ -16474,7 +16541,7 @@
       </c>
       <c r="J155" t="str">
         <f t="shared" si="2"/>
-        <v>(153, 'SOL'),</v>
+        <v>	(153, 'SOL'),</v>
       </c>
     </row>
     <row r="156" spans="7:10">
@@ -16489,7 +16556,7 @@
       </c>
       <c r="J156" t="str">
         <f t="shared" si="2"/>
-        <v>(154, 'PUR'),</v>
+        <v>	(154, 'PUR'),</v>
       </c>
     </row>
     <row r="157" spans="7:10">
@@ -16504,7 +16571,7 @@
       </c>
       <c r="J157" t="str">
         <f t="shared" si="2"/>
-        <v>(155, 'FIJ'),</v>
+        <v>	(155, 'FIJ'),</v>
       </c>
     </row>
     <row r="158" spans="7:10">
@@ -16519,7 +16586,7 @@
       </c>
       <c r="J158" t="str">
         <f t="shared" si="2"/>
-        <v>(156, 'HKG'),</v>
+        <v>	(156, 'HKG'),</v>
       </c>
     </row>
     <row r="159" spans="7:10">
@@ -16534,7 +16601,7 @@
       </c>
       <c r="J159" t="str">
         <f t="shared" si="2"/>
-        <v>(157, 'TAH'),</v>
+        <v>	(157, 'TAH'),</v>
       </c>
     </row>
     <row r="160" spans="7:10">
@@ -16549,7 +16616,7 @@
       </c>
       <c r="J160" t="str">
         <f t="shared" si="2"/>
-        <v>(158, 'MYA'),</v>
+        <v>	(158, 'MYA'),</v>
       </c>
     </row>
     <row r="161" spans="7:10">
@@ -16564,7 +16631,7 @@
       </c>
       <c r="J161" t="str">
         <f t="shared" si="2"/>
-        <v>(159, 'MDA'),</v>
+        <v>	(159, 'MDA'),</v>
       </c>
     </row>
     <row r="162" spans="7:10">
@@ -16579,7 +16646,7 @@
       </c>
       <c r="J162" t="str">
         <f t="shared" si="2"/>
-        <v>(160, 'VAN'),</v>
+        <v>	(160, 'VAN'),</v>
       </c>
     </row>
     <row r="163" spans="7:10">
@@ -16594,7 +16661,7 @@
       </c>
       <c r="J163" t="str">
         <f t="shared" si="2"/>
-        <v>(161, 'MLT'),</v>
+        <v>	(161, 'MLT'),</v>
       </c>
     </row>
     <row r="164" spans="7:10">
@@ -16609,7 +16676,7 @@
       </c>
       <c r="J164" t="str">
         <f t="shared" si="2"/>
-        <v>(162, 'ATG'),</v>
+        <v>	(162, 'ATG'),</v>
       </c>
     </row>
     <row r="165" spans="7:10">
@@ -16624,7 +16691,7 @@
       </c>
       <c r="J165" t="str">
         <f t="shared" si="2"/>
-        <v>(163, 'GRN'),</v>
+        <v>	(163, 'GRN'),</v>
       </c>
     </row>
     <row r="166" spans="7:10">
@@ -16639,7 +16706,7 @@
       </c>
       <c r="J166" t="str">
         <f t="shared" si="2"/>
-        <v>(164, 'CUB'),</v>
+        <v>	(164, 'CUB'),</v>
       </c>
     </row>
     <row r="167" spans="7:10">
@@ -16654,7 +16721,7 @@
       </c>
       <c r="J167" t="str">
         <f t="shared" si="2"/>
-        <v>(165, 'SWZ'),</v>
+        <v>	(165, 'SWZ'),</v>
       </c>
     </row>
     <row r="168" spans="7:10">
@@ -16669,7 +16736,7 @@
       </c>
       <c r="J168" t="str">
         <f t="shared" si="2"/>
-        <v>(166, 'LCA'),</v>
+        <v>	(166, 'LCA'),</v>
       </c>
     </row>
     <row r="169" spans="7:10">
@@ -16684,7 +16751,7 @@
       </c>
       <c r="J169" t="str">
         <f t="shared" si="2"/>
-        <v>(167, 'BMU'),</v>
+        <v>	(167, 'BMU'),</v>
       </c>
     </row>
     <row r="170" spans="7:10">
@@ -16699,7 +16766,7 @@
       </c>
       <c r="J170" t="str">
         <f t="shared" si="2"/>
-        <v>(168, 'PNG'),</v>
+        <v>	(168, 'PNG'),</v>
       </c>
     </row>
     <row r="171" spans="7:10">
@@ -16714,7 +16781,7 @@
       </c>
       <c r="J171" t="str">
         <f t="shared" si="2"/>
-        <v>(169, 'SSD'),</v>
+        <v>	(169, 'SSD'),</v>
       </c>
     </row>
     <row r="172" spans="7:10">
@@ -16729,7 +16796,7 @@
       </c>
       <c r="J172" t="str">
         <f t="shared" si="2"/>
-        <v>(170, 'VCT'),</v>
+        <v>	(170, 'VCT'),</v>
       </c>
     </row>
     <row r="173" spans="7:10">
@@ -16744,7 +16811,7 @@
       </c>
       <c r="J173" t="str">
         <f t="shared" si="2"/>
-        <v>(171, 'AFG'),</v>
+        <v>	(171, 'AFG'),</v>
       </c>
     </row>
     <row r="174" spans="7:10">
@@ -16759,7 +16826,7 @@
       </c>
       <c r="J174" t="str">
         <f t="shared" si="2"/>
-        <v>(172, 'AND'),</v>
+        <v>	(172, 'AND'),</v>
       </c>
     </row>
     <row r="175" spans="7:10">
@@ -16774,7 +16841,7 @@
       </c>
       <c r="J175" t="str">
         <f t="shared" si="2"/>
-        <v>(173, 'MDV'),</v>
+        <v>	(173, 'MDV'),</v>
       </c>
     </row>
     <row r="176" spans="7:10">
@@ -16789,7 +16856,7 @@
       </c>
       <c r="J176" t="str">
         <f t="shared" si="2"/>
-        <v>(174, 'TPE'),</v>
+        <v>	(174, 'TPE'),</v>
       </c>
     </row>
     <row r="177" spans="7:10">
@@ -16804,7 +16871,7 @@
       </c>
       <c r="J177" t="str">
         <f t="shared" si="2"/>
-        <v>(175, 'CAM'),</v>
+        <v>	(175, 'CAM'),</v>
       </c>
     </row>
     <row r="178" spans="7:10">
@@ -16819,7 +16886,7 @@
       </c>
       <c r="J178" t="str">
         <f t="shared" si="2"/>
-        <v>(176, 'MSR'),</v>
+        <v>	(176, 'MSR'),</v>
       </c>
     </row>
     <row r="179" spans="7:10">
@@ -16834,7 +16901,7 @@
       </c>
       <c r="J179" t="str">
         <f t="shared" si="2"/>
-        <v>(177, 'NEP'),</v>
+        <v>	(177, 'NEP'),</v>
       </c>
     </row>
     <row r="180" spans="7:10">
@@ -16849,7 +16916,7 @@
       </c>
       <c r="J180" t="str">
         <f t="shared" si="2"/>
-        <v>(178, 'MRI'),</v>
+        <v>	(178, 'MRI'),</v>
       </c>
     </row>
     <row r="181" spans="7:10">
@@ -16864,7 +16931,7 @@
       </c>
       <c r="J181" t="str">
         <f t="shared" si="2"/>
-        <v>(179, 'BAR'),</v>
+        <v>	(179, 'BAR'),</v>
       </c>
     </row>
     <row r="182" spans="7:10">
@@ -16879,7 +16946,7 @@
       </c>
       <c r="J182" t="str">
         <f t="shared" si="2"/>
-        <v>(180, 'BLZ'),</v>
+        <v>	(180, 'BLZ'),</v>
       </c>
     </row>
     <row r="183" spans="7:10">
@@ -16894,7 +16961,7 @@
       </c>
       <c r="J183" t="str">
         <f t="shared" si="2"/>
-        <v>(181, 'BAN'),</v>
+        <v>	(181, 'BAN'),</v>
       </c>
     </row>
     <row r="184" spans="7:10">
@@ -16909,7 +16976,7 @@
       </c>
       <c r="J184" t="str">
         <f t="shared" si="2"/>
-        <v>(182, 'DMA'),</v>
+        <v>	(182, 'DMA'),</v>
       </c>
     </row>
     <row r="185" spans="7:10">
@@ -16924,7 +16991,7 @@
       </c>
       <c r="J185" t="str">
         <f t="shared" si="2"/>
-        <v>(183, 'CHA'),</v>
+        <v>	(183, 'CHA'),</v>
       </c>
     </row>
     <row r="186" spans="7:10">
@@ -16939,7 +17006,7 @@
       </c>
       <c r="J186" t="str">
         <f t="shared" si="2"/>
-        <v>(184, 'ERI'),</v>
+        <v>	(184, 'ERI'),</v>
       </c>
     </row>
     <row r="187" spans="7:10">
@@ -16954,7 +17021,7 @@
       </c>
       <c r="J187" t="str">
         <f t="shared" si="2"/>
-        <v>(185, 'LAO'),</v>
+        <v>	(185, 'LAO'),</v>
       </c>
     </row>
     <row r="188" spans="7:10">
@@ -16969,7 +17036,7 @@
       </c>
       <c r="J188" t="str">
         <f t="shared" si="2"/>
-        <v>(186, 'COK'),</v>
+        <v>	(186, 'COK'),</v>
       </c>
     </row>
     <row r="189" spans="7:10">
@@ -16984,7 +17051,7 @@
       </c>
       <c r="J189" t="str">
         <f t="shared" si="2"/>
-        <v>(187, 'SRI'),</v>
+        <v>	(187, 'SRI'),</v>
       </c>
     </row>
     <row r="190" spans="7:10">
@@ -16999,7 +17066,7 @@
       </c>
       <c r="J190" t="str">
         <f t="shared" si="2"/>
-        <v>(188, 'SAM'),</v>
+        <v>	(188, 'SAM'),</v>
       </c>
     </row>
     <row r="191" spans="7:10">
@@ -17014,7 +17081,7 @@
       </c>
       <c r="J191" t="str">
         <f t="shared" si="2"/>
-        <v>(189, 'ARU'),</v>
+        <v>	(189, 'ARU'),</v>
       </c>
     </row>
     <row r="192" spans="7:10">
@@ -17029,7 +17096,7 @@
       </c>
       <c r="J192" t="str">
         <f t="shared" si="2"/>
-        <v>(190, 'MNG'),</v>
+        <v>	(190, 'MNG'),</v>
       </c>
     </row>
     <row r="193" spans="7:10">
@@ -17044,7 +17111,7 @@
       </c>
       <c r="J193" t="str">
         <f t="shared" si="2"/>
-        <v>(191, 'ASA'),</v>
+        <v>	(191, 'ASA'),</v>
       </c>
     </row>
     <row r="194" spans="7:10">
@@ -17059,7 +17126,7 @@
       </c>
       <c r="J194" t="str">
         <f t="shared" si="2"/>
-        <v>(192, 'BHU'),</v>
+        <v>	(192, 'BHU'),</v>
       </c>
     </row>
     <row r="195" spans="7:10">
@@ -17073,8 +17140,8 @@
         <v>732</v>
       </c>
       <c r="J195" t="str">
-        <f t="shared" ref="J195:J212" si="3">CHAR(9)&amp;"("&amp;G195&amp;", '"&amp;H195&amp;"'), "</f>
-        <v>(193, 'MAC'),</v>
+        <f t="shared" ref="J195:J212" si="3">CHAR(9)&amp;"("&amp;G195&amp;", '"&amp;H195&amp;"'),"</f>
+        <v>	(193, 'MAC'),</v>
       </c>
     </row>
     <row r="196" spans="7:10">
@@ -17089,7 +17156,7 @@
       </c>
       <c r="J196" t="str">
         <f t="shared" si="3"/>
-        <v>(194, 'BRU'),</v>
+        <v>	(194, 'BRU'),</v>
       </c>
     </row>
     <row r="197" spans="7:10">
@@ -17104,7 +17171,7 @@
       </c>
       <c r="J197" t="str">
         <f t="shared" si="3"/>
-        <v>(195, 'STP'),</v>
+        <v>	(195, 'STP'),</v>
       </c>
     </row>
     <row r="198" spans="7:10">
@@ -17119,7 +17186,7 @@
       </c>
       <c r="J198" t="str">
         <f t="shared" si="3"/>
-        <v>(196, 'DJI'),</v>
+        <v>	(196, 'DJI'),</v>
       </c>
     </row>
     <row r="199" spans="7:10">
@@ -17134,7 +17201,7 @@
       </c>
       <c r="J199" t="str">
         <f t="shared" si="3"/>
-        <v>(197, 'CAY'),</v>
+        <v>	(197, 'CAY'),</v>
       </c>
     </row>
     <row r="200" spans="7:10">
@@ -17149,7 +17216,7 @@
       </c>
       <c r="J200" t="str">
         <f t="shared" si="3"/>
-        <v>(198, 'PAK'),</v>
+        <v>	(198, 'PAK'),</v>
       </c>
     </row>
     <row r="201" spans="7:10">
@@ -17164,7 +17231,7 @@
       </c>
       <c r="J201" t="str">
         <f t="shared" si="3"/>
-        <v>(199, 'SOM'),</v>
+        <v>	(199, 'SOM'),</v>
       </c>
     </row>
     <row r="202" spans="7:10">
@@ -17179,7 +17246,7 @@
       </c>
       <c r="J202" t="str">
         <f t="shared" si="3"/>
-        <v>(200, 'TGA'),</v>
+        <v>	(200, 'TGA'),</v>
       </c>
     </row>
     <row r="203" spans="7:10">
@@ -17194,7 +17261,7 @@
       </c>
       <c r="J203" t="str">
         <f t="shared" si="3"/>
-        <v>(201, 'TLS'),</v>
+        <v>	(201, 'TLS'),</v>
       </c>
     </row>
     <row r="204" spans="7:10">
@@ -17209,7 +17276,7 @@
       </c>
       <c r="J204" t="str">
         <f t="shared" si="3"/>
-        <v>(202, 'GIB'),</v>
+        <v>	(202, 'GIB'),</v>
       </c>
     </row>
     <row r="205" spans="7:10">
@@ -17224,7 +17291,7 @@
       </c>
       <c r="J205" t="str">
         <f t="shared" si="3"/>
-        <v>(203, 'GUM'),</v>
+        <v>	(203, 'GUM'),</v>
       </c>
     </row>
     <row r="206" spans="7:10">
@@ -17239,7 +17306,7 @@
       </c>
       <c r="J206" t="str">
         <f t="shared" si="3"/>
-        <v>(204, 'SEY'),</v>
+        <v>	(204, 'SEY'),</v>
       </c>
     </row>
     <row r="207" spans="7:10">
@@ -17254,7 +17321,7 @@
       </c>
       <c r="J207" t="str">
         <f t="shared" si="3"/>
-        <v>(205, 'TCA'),</v>
+        <v>	(205, 'TCA'),</v>
       </c>
     </row>
     <row r="208" spans="7:10">
@@ -17269,7 +17336,7 @@
       </c>
       <c r="J208" t="str">
         <f t="shared" si="3"/>
-        <v>(206, 'LIE'),</v>
+        <v>	(206, 'LIE'),</v>
       </c>
     </row>
     <row r="209" spans="7:10">
@@ -17284,7 +17351,7 @@
       </c>
       <c r="J209" t="str">
         <f t="shared" si="3"/>
-        <v>(207, 'BAH'),</v>
+        <v>	(207, 'BAH'),</v>
       </c>
     </row>
     <row r="210" spans="7:10">
@@ -17299,7 +17366,7 @@
       </c>
       <c r="J210" t="str">
         <f t="shared" si="3"/>
-        <v>(208, 'VIR'),</v>
+        <v>	(208, 'VIR'),</v>
       </c>
     </row>
     <row r="211" spans="7:10">
@@ -17314,7 +17381,7 @@
       </c>
       <c r="J211" t="str">
         <f t="shared" si="3"/>
-        <v>(209, 'VGB'),</v>
+        <v>	(209, 'VGB'),</v>
       </c>
     </row>
     <row r="212" spans="7:10">
@@ -17329,7 +17396,7 @@
       </c>
       <c r="J212" t="str">
         <f t="shared" si="3"/>
-        <v>(210, 'AIA'),</v>
+        <v>	(210, 'AIA'),</v>
       </c>
     </row>
     <row r="213" spans="7:10">
